--- a/evaluate/测试集.xlsx
+++ b/evaluate/测试集.xlsx
@@ -399,7 +399,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,13 +438,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -915,152 +908,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1069,9 +1062,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1464,1203 +1454,1203 @@
     <col min="4" max="4" width="41.7211538461538" style="3" customWidth="1"/>
     <col min="5" max="5" width="39.0096153846154" style="2" customWidth="1"/>
     <col min="6" max="18" width="12.4326923076923" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="4"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>45485</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>42730</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>45289</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>42730</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>44967</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>44467</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>44826</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>45098</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>45476</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>45412</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
+      <c r="E18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>45318</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
+      <c r="E19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>44302</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>42671</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>45527</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+      <c r="E22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>44826</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>42957</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>45504</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>45534</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
+      <c r="E26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>43189</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
+      <c r="E27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>45520</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>44826</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
+      <c r="E29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>45411</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>45423</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>44620</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
+      <c r="E32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>43007</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>45289</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
+      <c r="E34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>45240</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>45043</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>44923</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
+      <c r="E37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>45565</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>45477</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
+      <c r="E39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
     </row>
     <row r="40" ht="20.25" customHeight="1" spans="1:18">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13" t="s">
+      <c r="A40" s="12"/>
+      <c r="B40" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41" ht="34" customHeight="1" spans="1:18">
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="42" ht="35" customHeight="1" spans="1:18">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>117</v>
       </c>
     </row>

--- a/evaluate/测试集.xlsx
+++ b/evaluate/测试集.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
   <si>
     <t>专利申请号</t>
   </si>
@@ -71,42 +71,6 @@
     <t>2019.06.21</t>
   </si>
   <si>
-    <t>CN202210017491.5</t>
-  </si>
-  <si>
-    <t>CN114256551B</t>
-  </si>
-  <si>
-    <t>蜂巢能源 L600 / 196Ah LFP 短刀电芯（21.5×574×118mm，627.3Wh）</t>
-  </si>
-  <si>
-    <t>CN202210244592.6</t>
-  </si>
-  <si>
-    <t>CN114512760B</t>
-  </si>
-  <si>
-    <t>蜂巢能源 L600 / 196Ah LFP 短刀电芯（21.5×574×118mm，627.4Wh）</t>
-  </si>
-  <si>
-    <t>CN202210244489.1</t>
-  </si>
-  <si>
-    <t>CN114512758B</t>
-  </si>
-  <si>
-    <t>蜂巢能源 L600 / 196Ah LFP 短刀电芯（21.5×574×118mm，627.5Wh）</t>
-  </si>
-  <si>
-    <t>CN202210555862.5</t>
-  </si>
-  <si>
-    <t>CN115020886B</t>
-  </si>
-  <si>
-    <t>蜂巢能源 L600 / 196Ah LFP 短刀电芯（21.5×574×118mm，627.6Wh）</t>
-  </si>
-  <si>
     <t>CN202421648348.7</t>
   </si>
   <si>
@@ -269,100 +233,28 @@
     <t>问界 M8 2025款 纯电版、增程版</t>
   </si>
   <si>
-    <t>CN201820465067.6</t>
-  </si>
-  <si>
-    <t>CN208515692U</t>
-  </si>
-  <si>
-    <t>赛力斯 问界M9 2024款</t>
-  </si>
-  <si>
-    <t>CN202421999220.5</t>
-  </si>
-  <si>
-    <t>CN222988255U</t>
-  </si>
-  <si>
-    <t>中版 蔚来 ES8 纯电动 2026款</t>
-  </si>
-  <si>
     <t>中版 问界 M8 增程式 2025款;中版 零跑 B10 纯电动 2025款</t>
   </si>
   <si>
     <t>领克900</t>
   </si>
   <si>
-    <t>CN202421022054.3</t>
-  </si>
-  <si>
-    <t>CN222346846U</t>
-  </si>
-  <si>
-    <t>奔驰S级2026款</t>
-  </si>
-  <si>
-    <t>CN202220433147.X</t>
-  </si>
-  <si>
-    <t>CN216969302U</t>
-  </si>
-  <si>
-    <t>吉利银河E5 2024款</t>
-  </si>
-  <si>
-    <t>CN201710910193.8</t>
-  </si>
-  <si>
-    <t>CN109586447B</t>
-  </si>
-  <si>
-    <t>CN202323668649.4</t>
-  </si>
-  <si>
-    <t>CN222025607U</t>
+    <t>CN202422415442.4</t>
+  </si>
+  <si>
+    <t>CN223085813U</t>
+  </si>
+  <si>
+    <t>中版 吉利 银河M9 插电混动 2025款</t>
+  </si>
+  <si>
+    <t>CN202421576298.6</t>
+  </si>
+  <si>
+    <t>CN222577204U</t>
   </si>
   <si>
     <t>中版 问界 M8 增程式 2025款</t>
-  </si>
-  <si>
-    <t>CN202323054149.1</t>
-  </si>
-  <si>
-    <t>CN221349505U</t>
-  </si>
-  <si>
-    <t>小鹏GX</t>
-  </si>
-  <si>
-    <t>CN202321016546.7</t>
-  </si>
-  <si>
-    <t>CN219841035U</t>
-  </si>
-  <si>
-    <t>中版 小米 SU7 2024款</t>
-  </si>
-  <si>
-    <t>CN202223505512.2</t>
-  </si>
-  <si>
-    <t>CN219492030U</t>
-  </si>
-  <si>
-    <t>CN202422415442.4</t>
-  </si>
-  <si>
-    <t>CN223085813U</t>
-  </si>
-  <si>
-    <t>中版 吉利 银河M9 插电混动 2025款</t>
-  </si>
-  <si>
-    <t>CN202421576298.6</t>
-  </si>
-  <si>
-    <t>CN222577204U</t>
   </si>
   <si>
     <t>CN110293961B</t>
@@ -399,7 +291,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,36 +300,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -908,193 +782,193 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1445,8 +1319,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:R39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="42.8653846153846" style="2" customWidth="1"/>
     <col min="2" max="2" width="36.2884615384615" style="2" customWidth="1"/>
@@ -1454,10 +1328,10 @@
     <col min="4" max="4" width="41.7211538461538" style="3" customWidth="1"/>
     <col min="5" max="5" width="39.0096153846154" style="2" customWidth="1"/>
     <col min="6" max="18" width="12.4326923076923" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="19" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1487,17 +1361,17 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="2" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -1517,7 +1391,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -1527,7 +1401,7 @@
       <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -1547,7 +1421,7 @@
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="4" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -1557,8 +1431,8 @@
       <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>13</v>
+      <c r="D4" s="9">
+        <v>45485</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>9</v>
@@ -1577,7 +1451,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="5" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
@@ -1587,8 +1461,8 @@
       <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>13</v>
+      <c r="D5" s="9">
+        <v>42730</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
@@ -1607,7 +1481,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="6" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -1617,8 +1491,8 @@
       <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>13</v>
+      <c r="D6" s="9">
+        <v>45289</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>9</v>
@@ -1637,7 +1511,7 @@
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="7" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
@@ -1647,8 +1521,8 @@
       <c r="C7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>13</v>
+      <c r="D7" s="9">
+        <v>42730</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>9</v>
@@ -1667,7 +1541,7 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="8" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
@@ -1678,7 +1552,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="9">
-        <v>45485</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>9</v>
@@ -1697,7 +1571,7 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="9" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
@@ -1705,10 +1579,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D9" s="9">
-        <v>42730</v>
+        <v>44467</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>9</v>
@@ -1727,18 +1601,18 @@
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="10" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="D10" s="9">
-        <v>45289</v>
+        <v>44826</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>9</v>
@@ -1757,18 +1631,18 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="11" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" s="9">
-        <v>42730</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>9</v>
@@ -1787,7 +1661,7 @@
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="12" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
@@ -1798,7 +1672,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="9">
-        <v>44967</v>
+        <v>45098</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>9</v>
@@ -1817,18 +1691,18 @@
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="13" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D13" s="9">
-        <v>44467</v>
+        <v>45476</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>9</v>
@@ -1847,18 +1721,18 @@
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="14" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="C14" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="D14" s="9">
-        <v>44826</v>
+        <v>45412</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>9</v>
@@ -1877,18 +1751,18 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="15" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>49</v>
+      </c>
+      <c r="D15" s="9">
+        <v>45318</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>9</v>
@@ -1907,7 +1781,7 @@
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="16" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A16" s="7" t="s">
         <v>50</v>
       </c>
@@ -1918,7 +1792,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="9">
-        <v>45098</v>
+        <v>44302</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>9</v>
@@ -1937,18 +1811,18 @@
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="17" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A17" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D17" s="9">
-        <v>45476</v>
+        <v>42671</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>9</v>
@@ -1967,18 +1841,18 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="18" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A18" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>58</v>
+      <c r="C18" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="D18" s="9">
-        <v>45412</v>
+        <v>45527</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>9</v>
@@ -1997,18 +1871,18 @@
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="19" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A19" s="7" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>61</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="D19" s="9">
-        <v>45318</v>
+        <v>44826</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>9</v>
@@ -2027,18 +1901,18 @@
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="20" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A20" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="D20" s="9">
-        <v>44302</v>
+        <v>42957</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>9</v>
@@ -2057,18 +1931,18 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="21" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A21" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="D21" s="9">
-        <v>42671</v>
+        <v>45504</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>9</v>
@@ -2087,18 +1961,18 @@
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="22" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A22" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>58</v>
+        <v>66</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="D22" s="9">
-        <v>45527</v>
+        <v>45534</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>9</v>
@@ -2117,15 +1991,15 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="23" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A23" s="7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>70</v>
+        <v>32</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="D23" s="9">
         <v>44826</v>
@@ -2147,18 +2021,18 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="24" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A24" s="7" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>73</v>
+        <v>35</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="D24" s="9">
-        <v>42957</v>
+        <v>45411</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>9</v>
@@ -2177,18 +2051,18 @@
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="30" customHeight="1" spans="1:18">
+    <row r="25" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="D25" s="9">
-        <v>45504</v>
+        <v>45565</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>9</v>
@@ -2207,18 +2081,18 @@
       <c r="Q25" s="6"/>
       <c r="R25" s="6"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
+    <row r="26" s="1" customFormat="1" ht="18" spans="1:18">
       <c r="A26" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="D26" s="9">
-        <v>45534</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>9</v>
@@ -2237,431 +2111,50 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A27" s="7" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:18">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:18">
+      <c r="B28" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" spans="1:18">
+      <c r="B29" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C29" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="11" t="s">
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:18">
+      <c r="B30" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="9">
-        <v>43189</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A28" s="7" t="s">
+      <c r="C30" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="9">
-        <v>45520</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="9">
-        <v>44826</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A30" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="9">
-        <v>45411</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="9">
-        <v>45423</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A32" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="9">
-        <v>44620</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="9">
-        <v>43007</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A34" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="9">
-        <v>45289</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="9">
-        <v>45240</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" s="9">
-        <v>45043</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" s="9">
-        <v>44923</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A38" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="9">
-        <v>45565</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:18">
-      <c r="A39" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="9">
-        <v>45477</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-    </row>
-    <row r="40" ht="20.25" customHeight="1" spans="1:18">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="12"/>
-    </row>
-    <row r="41" ht="34" customHeight="1" spans="1:18">
-      <c r="B41" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" ht="35" customHeight="1" spans="1:18">
-      <c r="B42" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" ht="31" customHeight="1" spans="1:18">
-      <c r="B43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
+    </row>
+    <row r="31" s="1" customFormat="1"/>
+    <row r="32" s="1" customFormat="1"/>
+    <row r="33" s="1" customFormat="1"/>
+    <row r="34" s="1" customFormat="1"/>
+    <row r="35" s="1" customFormat="1"/>
+    <row r="36" s="1" customFormat="1"/>
+    <row r="37" s="1" customFormat="1"/>
+    <row r="38" s="1" customFormat="1"/>
+    <row r="39" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
